--- a/site/public/DwellingDamageProfile-template.xlsx
+++ b/site/public/DwellingDamageProfile-template.xlsx
@@ -152,45 +152,130 @@
   <commentList>
     <comment ref="A1" authorId="0" shapeId="0">
       <text>
+        <t>Identifiers carried by this entity, such as national ID numbers, program IDs, or identifiers asserted by an identity document.</t>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0" shapeId="0">
+      <text>
+        <t>The person or group that the profile or scoring event is about. Ranged at Party (not Agent) because Profiles observe receivers: persons and organised groups of persons (Household, Family, Farm). Institutional actors (Organizations) are described through their own Organization records, not as subjects of a Profile.</t>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0">
+      <text>
+        <t>The date on which the profile data was collected (when the instrument was administered or the measurement taken).</t>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0" shapeId="0">
+      <text>
+        <t>The agent (enumerator, field officer, or agency) accountable for administering the instrument or taking the measurement. Typically a Person or an Organization. When a software tool captured or derived the data, record it separately as software_used; performed_by identifies who is responsible, not what ran the capture.</t>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0">
+      <text>
+        <t>Reference to the instrument (survey form, questionnaire, screening protocol, measurement procedure) administered in this profile record.</t>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0" shapeId="0">
+      <text>
+        <t>The software that performed this step, recorded so the result can be reproduced or audited. Distinct from the accountable evaluator or performer (the person or organisation responsible), which is recorded separately.</t>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="0" shapeId="0">
+      <text>
+        <t>How the instrument was administered to the subject: self-report, proxy-report (someone else answering about the subject), assisted (the subject answering with help), or mixed. Washington Group analytical guidance recommends disaggregating prevalence by administration mode because proxy responses systematically underreport difficulty.</t>
+      </text>
+    </comment>
+    <comment ref="H1" authorId="0" shapeId="0">
+      <text>
+        <t>The person who provided the answers to the instrument, when different from the subject. Required whenever the administration mode is proxy or assisted.</t>
+      </text>
+    </comment>
+    <comment ref="I1" authorId="0" shapeId="0">
+      <text>
+        <t>The relationship of the respondent to the subject (parent, spouse, guardian, caregiver, etc.). Uses relationship-type because it describes a person-to-person relationship, not a role within a group. Required whenever the administration mode is proxy or assisted.</t>
+      </text>
+    </comment>
+    <comment ref="J1" authorId="0" shapeId="0">
+      <text>
+        <t>The PublicSchema property IDs that were actually asked during this administration. Lets adopters distinguish items that were asked and declined (answer absent) from items that were not asked at all. When omitted, the item set is assumed to be the default item_set of the instrument used. The intended producer is the form compiler or collection server, which populates this list from the form definition at submission time.</t>
+      </text>
+    </comment>
+    <comment ref="K1" authorId="0" shapeId="0">
+      <text>
+        <t>The type of dwelling occupied by the household (e.g., permanent structure, temporary shelter, shared housing).</t>
+      </text>
+    </comment>
+    <comment ref="L1" authorId="0" shapeId="0">
+      <text>
+        <t>The primary material of the floor in the household's dwelling.</t>
+      </text>
+    </comment>
+    <comment ref="M1" authorId="0" shapeId="0">
+      <text>
+        <t>The primary material of the exterior walls in the household's dwelling.</t>
+      </text>
+    </comment>
+    <comment ref="N1" authorId="0" shapeId="0">
+      <text>
+        <t>The primary material of the roof in the household's dwelling.</t>
+      </text>
+    </comment>
+    <comment ref="O1" authorId="0" shapeId="0">
+      <text>
+        <t>The main source of drinking water used by the household.</t>
+      </text>
+    </comment>
+    <comment ref="P1" authorId="0" shapeId="0">
+      <text>
+        <t>The type of toilet or sanitation facility used by the household.</t>
+      </text>
+    </comment>
+    <comment ref="Q1" authorId="0" shapeId="0">
+      <text>
+        <t>Whether the household has access to electricity from any source.</t>
+      </text>
+    </comment>
+    <comment ref="R1" authorId="0" shapeId="0">
+      <text>
         <t>Severity of physical damage to the assessed dwelling, observed during a post-shock structural assessment. Recorded against a standardized five-tier scale aligned with IOM Displacement Tracking Matrix labels.</t>
       </text>
     </comment>
-    <comment ref="B1" authorId="0" shapeId="0">
+    <comment ref="S1" authorId="0" shapeId="0">
       <text>
         <t>Programming-facing judgement of whether the assessed dwelling can currently be occupied and what category of shelter response it requires. Distinct from damage_level: a moderately damaged structure may still be habitable, and a lightly damaged one may be vacated for other reasons.</t>
       </text>
     </comment>
-    <comment ref="C1" authorId="0" shapeId="0">
+    <comment ref="T1" authorId="0" shapeId="0">
       <text>
         <t>Type of shelter arrangement the household is currently occupying at the time of assessment. Complements dwelling_type (which records the household's usual dwelling) by recording where the household is actually living now, particularly when the original dwelling is damaged, inaccessible, or vacated.</t>
       </text>
     </comment>
-    <comment ref="D1" authorId="0" shapeId="0">
+    <comment ref="U1" authorId="0" shapeId="0">
       <text>
         <t>Optional structural safety tag assigned by a qualified engineer or trained shelter assessor, using the ATC-20 green/yellow/red taxonomy. Frequently null: a household enumerator is not expected to assign a structural safety tag, and many post-shock administrations do not include a structural inspector visit.</t>
       </text>
     </comment>
-    <comment ref="E1" authorId="0" shapeId="0">
+    <comment ref="V1" authorId="0" shapeId="0">
       <text>
         <t>Categories of non-food items the household currently lacks and would need to meet minimum shelter and settlement standards. Multi-select across the Sphere 2018 minimum NFI package.</t>
       </text>
     </comment>
-    <comment ref="F1" authorId="0" shapeId="0">
+    <comment ref="W1" authorId="0" shapeId="0">
       <text>
         <t>The household's stated intent regarding the damaged dwelling: repair in place, rebuild in place, relocate, unable to act without external support, or undecided. Used by recovery programming to target repair grants, reconstruction grants, and relocation assistance.</t>
       </text>
     </comment>
-    <comment ref="G1" authorId="0" shapeId="0">
+    <comment ref="X1" authorId="0" shapeId="0">
       <text>
         <t>Essential services (water, sanitation, electricity, telecommunications) that are currently degraded at the household's dwelling after the shock. Multi-select. Codes cover both full outage and partial-function cases: water may be absent, intermittent, or present-but-unsafe; sanitation may be unusable or present-but-overflowing; electricity may be absent or intermittent. Distinct from the household's baseline service infrastructure type, which is recorded by water_source, sanitation_facility, and electricity_access.</t>
       </text>
     </comment>
-    <comment ref="H1" authorId="0" shapeId="0">
+    <comment ref="Y1" authorId="0" shapeId="0">
       <text>
         <t>The hazard event that triggered this record. On DwellingDamageProfile the referenced HazardEvent identifies the flood, earthquake, cyclone, drought, conflict event, or other shock the post-shock assessment is responding to. A record may omit this property when the damage is chronic or not attributable to a single event.</t>
       </text>
     </comment>
-    <comment ref="I1" authorId="0" shapeId="0">
+    <comment ref="Z1" authorId="0" shapeId="0">
       <text>
         <t>The physical location where the post-shock assessment was carried out, typically the location of the assessed dwelling. Distinct from Household.location (which is the household's registered administrative or coordinate location): the two may differ if the household has displaced, relocated, or is temporarily sheltering elsewhere while the assessed structure remains at its registered site.</t>
       </text>
@@ -489,62 +574,164 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:Z2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
-    <col width="31" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
-    <col width="21" customWidth="1" min="7" max="7"/>
-    <col width="26" customWidth="1" min="8" max="8"/>
-    <col width="25" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="26" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="17" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="15" customWidth="1" min="15" max="15"/>
+    <col width="22" customWidth="1" min="16" max="16"/>
+    <col width="21" customWidth="1" min="17" max="17"/>
+    <col width="15" customWidth="1" min="18" max="18"/>
+    <col width="22" customWidth="1" min="19" max="19"/>
+    <col width="23" customWidth="1" min="20" max="20"/>
+    <col width="31" customWidth="1" min="21" max="21"/>
+    <col width="26" customWidth="1" min="22" max="22"/>
+    <col width="24" customWidth="1" min="23" max="23"/>
+    <col width="21" customWidth="1" min="24" max="24"/>
+    <col width="26" customWidth="1" min="25" max="25"/>
+    <col width="25" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>Identifiers</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Subject</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Observation date</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Performed by</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Instrument used</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Software used</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Administration mode</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Respondent</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Respondent relationship</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Items asked</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Dwelling type</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Floor material</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Wall material</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Roof material</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Water source</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Sanitation facility</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Electricity access</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
           <t>Damage level</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Habitability status</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Current shelter type</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Structural safety assessment</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Missing essential items</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Reconstruction intent</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Services disrupted</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Triggering hazard event</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Location of assessment</t>
         </is>
@@ -553,45 +740,130 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>identifiers</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>subject</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>observation_date</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>performed_by</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>instrument_used</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>software_used</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>administration_mode</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>respondent</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>respondent_relationship</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>items_asked</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>dwelling_type</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>floor_material</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>wall_material</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>roof_material</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>water_source</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>sanitation_facility</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>electricity_access</t>
+        </is>
+      </c>
+      <c r="R2" s="2" t="inlineStr">
+        <is>
           <t>damage_level</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="S2" s="2" t="inlineStr">
         <is>
           <t>habitability_status</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="T2" s="2" t="inlineStr">
         <is>
           <t>current_shelter_type</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="U2" s="2" t="inlineStr">
         <is>
           <t>structural_safety_assessment</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="V2" s="2" t="inlineStr">
         <is>
           <t>essential_items_missing</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="W2" s="2" t="inlineStr">
         <is>
           <t>reconstruction_intent</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="X2" s="2" t="inlineStr">
         <is>
           <t>services_disrupted</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="Y2" s="2" t="inlineStr">
         <is>
           <t>triggering_hazard_event</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="Z2" s="2" t="inlineStr">
         <is>
           <t>location_of_assessment</t>
         </is>
@@ -599,25 +871,25 @@
     </row>
   </sheetData>
   <dataValidations count="7">
-    <dataValidation sqref="A3:A1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Damage level" error="Value must be from the shelter-damage-level vocabulary." type="list">
+    <dataValidation sqref="R3:R1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Damage level" error="Value must be from the shelter-damage-level vocabulary." type="list">
       <formula1>_values!$A$2:$A$6</formula1>
     </dataValidation>
-    <dataValidation sqref="B3:B1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Habitability status" error="Value must be from the habitability-status vocabulary." type="list">
+    <dataValidation sqref="S3:S1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Habitability status" error="Value must be from the habitability-status vocabulary." type="list">
       <formula1>_values!$B$2:$B$6</formula1>
     </dataValidation>
-    <dataValidation sqref="C3:C1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Current shelter type" error="Value must be from the shelter-situation-type vocabulary." type="list">
+    <dataValidation sqref="T3:T1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Current shelter type" error="Value must be from the shelter-situation-type vocabulary." type="list">
       <formula1>_values!$C$2:$C$10</formula1>
     </dataValidation>
-    <dataValidation sqref="D3:D1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Structural safety assessment" error="Value must be from the structural-safety-tag vocabulary." type="list">
+    <dataValidation sqref="U3:U1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Structural safety assessment" error="Value must be from the structural-safety-tag vocabulary." type="list">
       <formula1>_values!$D$2:$D$4</formula1>
     </dataValidation>
-    <dataValidation sqref="E3:E1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Missing essential items" error="Value must be from the nfi-item-type vocabulary." type="list">
+    <dataValidation sqref="V3:V1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Missing essential items" error="Value must be from the nfi-item-type vocabulary." type="list">
       <formula1>_values!$E$2:$E$13</formula1>
     </dataValidation>
-    <dataValidation sqref="F3:F1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Reconstruction intent" error="Value must be from the reconstruction-intent vocabulary." type="list">
+    <dataValidation sqref="W3:W1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Reconstruction intent" error="Value must be from the reconstruction-intent vocabulary." type="list">
       <formula1>_values!$F$2:$F$6</formula1>
     </dataValidation>
-    <dataValidation sqref="G3:G1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Services disrupted" error="Value must be from the service-disruption-type vocabulary." type="list">
+    <dataValidation sqref="X3:X1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Services disrupted" error="Value must be from the service-disruption-type vocabulary." type="list">
       <formula1>_values!$G$2:$G$10</formula1>
     </dataValidation>
   </dataValidations>

--- a/site/public/DwellingDamageProfile-template.xlsx
+++ b/site/public/DwellingDamageProfile-template.xlsx
@@ -878,7 +878,7 @@
       <formula1>_values!$B$2:$B$6</formula1>
     </dataValidation>
     <dataValidation sqref="T3:T1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Current shelter type" error="Value must be from the shelter-situation-type vocabulary." type="list">
-      <formula1>_values!$C$2:$C$10</formula1>
+      <formula1>_values!$C$2:$C$12</formula1>
     </dataValidation>
     <dataValidation sqref="U3:U1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Structural safety assessment" error="Value must be from the structural-safety-tag vocabulary." type="list">
       <formula1>_values!$D$2:$D$4</formula1>
@@ -1188,6 +1188,11 @@
       </c>
     </row>
     <row r="11">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>camp_planned</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>hygiene_kit</t>
@@ -1195,6 +1200,11 @@
       </c>
     </row>
     <row r="12">
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>spontaneous_settlement</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>winterization_kit</t>

--- a/site/public/DwellingDamageProfile-template.xlsx
+++ b/site/public/DwellingDamageProfile-template.xlsx
@@ -884,7 +884,7 @@
       <formula1>_values!$D$2:$D$4</formula1>
     </dataValidation>
     <dataValidation sqref="V3:V1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Missing essential items" error="Value must be from the nfi-item-type vocabulary." type="list">
-      <formula1>_values!$E$2:$E$13</formula1>
+      <formula1>_values!$E$2:$E$23</formula1>
     </dataValidation>
     <dataValidation sqref="W3:W1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Reconstruction intent" error="Value must be from the reconstruction-intent vocabulary." type="list">
       <formula1>_values!$F$2:$F$6</formula1>
@@ -904,7 +904,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1214,6 +1214,76 @@
     <row r="13">
       <c r="E13" t="inlineStr">
         <is>
+          <t>cooking_pot</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>plate_or_bowl</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>cup_or_mug</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>kitchen_knife</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>matches_or_lighter</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>mosquito_net</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>clothing_adult</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>clothing_child</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>shelter_repair_tools</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>water_jerrycan</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="E23" t="inlineStr">
+        <is>
           <t>other</t>
         </is>
       </c>

--- a/site/public/DwellingDamageProfile-template.xlsx
+++ b/site/public/DwellingDamageProfile-template.xlsx
@@ -870,27 +870,51 @@
       </c>
     </row>
   </sheetData>
-  <dataValidations count="7">
+  <dataValidations count="15">
+    <dataValidation sqref="G3:G1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Administration mode" error="Value must be from the administration-mode vocabulary." type="list">
+      <formula1>_values!$A$2:$A$5</formula1>
+    </dataValidation>
+    <dataValidation sqref="I3:I1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Respondent relationship" error="Value must be from the relationship-type vocabulary." type="list">
+      <formula1>_values!$B$2:$B$16</formula1>
+    </dataValidation>
+    <dataValidation sqref="K3:K1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Dwelling type" error="Value must be from the dwelling-type vocabulary." type="list">
+      <formula1>_values!$C$2:$C$7</formula1>
+    </dataValidation>
+    <dataValidation sqref="L3:L1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Floor material" error="Value must be from the floor-material vocabulary." type="list">
+      <formula1>_values!$D$2:$D$11</formula1>
+    </dataValidation>
+    <dataValidation sqref="M3:M1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Wall material" error="Value must be from the wall-material vocabulary." type="list">
+      <formula1>_values!$E$2:$E$17</formula1>
+    </dataValidation>
+    <dataValidation sqref="N3:N1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Roof material" error="Value must be from the roof-material vocabulary." type="list">
+      <formula1>_values!$F$2:$F$15</formula1>
+    </dataValidation>
+    <dataValidation sqref="O3:O1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Water source" error="Value must be from the water-source vocabulary." type="list">
+      <formula1>_values!$G$2:$G$17</formula1>
+    </dataValidation>
+    <dataValidation sqref="P3:P1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Sanitation facility" error="Value must be from the sanitation-facility vocabulary." type="list">
+      <formula1>_values!$H$2:$H$14</formula1>
+    </dataValidation>
     <dataValidation sqref="R3:R1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Damage level" error="Value must be from the shelter-damage-level vocabulary." type="list">
-      <formula1>_values!$A$2:$A$6</formula1>
+      <formula1>_values!$I$2:$I$6</formula1>
     </dataValidation>
     <dataValidation sqref="S3:S1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Habitability status" error="Value must be from the habitability-status vocabulary." type="list">
-      <formula1>_values!$B$2:$B$6</formula1>
+      <formula1>_values!$J$2:$J$6</formula1>
     </dataValidation>
     <dataValidation sqref="T3:T1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Current shelter type" error="Value must be from the shelter-situation-type vocabulary." type="list">
-      <formula1>_values!$C$2:$C$12</formula1>
+      <formula1>_values!$K$2:$K$12</formula1>
     </dataValidation>
     <dataValidation sqref="U3:U1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Structural safety assessment" error="Value must be from the structural-safety-tag vocabulary." type="list">
-      <formula1>_values!$D$2:$D$4</formula1>
+      <formula1>_values!$L$2:$L$4</formula1>
     </dataValidation>
     <dataValidation sqref="V3:V1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Missing essential items" error="Value must be from the nfi-item-type vocabulary." type="list">
-      <formula1>_values!$E$2:$E$23</formula1>
+      <formula1>_values!$M$2:$M$23</formula1>
     </dataValidation>
     <dataValidation sqref="W3:W1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Reconstruction intent" error="Value must be from the reconstruction-intent vocabulary." type="list">
-      <formula1>_values!$F$2:$F$6</formula1>
+      <formula1>_values!$N$2:$N$6</formula1>
     </dataValidation>
     <dataValidation sqref="X3:X1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Services disrupted" error="Value must be from the service-disruption-type vocabulary." type="list">
-      <formula1>_values!$G$2:$G$10</formula1>
+      <formula1>_values!$O$2:$O$10</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -904,41 +928,81 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:O23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>administration_mode</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>respondent_relationship</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>dwelling_type</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>floor_material</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>wall_material</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>roof_material</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>water_source</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>sanitation_facility</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>damage_level</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>habitability_status</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>current_shelter_type</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>structural_safety_assessment</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>essential_items_missing</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>reconstruction_intent</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>services_disrupted</t>
         </is>
@@ -947,35 +1011,75 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>self</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>spouse</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>permanent</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>earth_sand</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>no_walls</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>no_roof</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>piped_into_dwelling</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>flush_to_piped_sewer</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
           <t>destroyed</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>habitable</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>original_home</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>safe</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>tarpaulin</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>repair_in_place</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>water</t>
         </is>
@@ -984,35 +1088,75 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>proxy</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>parent</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>semi_permanent</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>dung</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>cane_palm_trunks</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>thatch_palm_leaf</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>piped_to_yard</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>flush_to_septic_tank</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
           <t>severely_damaged</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>needs_minor_repairs</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>original_home_repaired</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>restricted_use</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>plastic_sheeting</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>rebuild_in_place</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>sanitation</t>
         </is>
@@ -1021,35 +1165,75 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>assisted</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>child</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>temporary</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>wood_planks</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>dirt</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>sod_grass</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>piped_to_neighbor</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>flush_to_pit_latrine</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
           <t>moderately_damaged</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>needs_major_repairs_uninhabitable</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>tent_or_emergency_shelter</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>unsafe</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>rope_fixings</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>relocate</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>electricity</t>
         </is>
@@ -1058,182 +1242,522 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>sibling</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>improvised</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>palm_bamboo</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>bamboo_with_mud</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>rustic_mat</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>public_tap_standpipe</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>flush_to_open_drain</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
           <t>minor_damage</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>must_be_demolished</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>transitional_shelter</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>blanket</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>cannot_act_without_support</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>telecommunications</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>grandparent</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>collective</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>parquet_polished_wood</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>stone_with_mud</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>palm_bamboo</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>tube_well_borehole</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>flush_to_unknown</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
         <is>
           <t>undamaged</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>collective_center</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>sleeping_mat</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>undecided</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>water_unsafe</t>
         </is>
       </c>
     </row>
     <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>grandchild</t>
+        </is>
+      </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>mobile</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>vinyl_asphalt</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>uncovered_adobe</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>wood_planks</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>protected_well</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>ventilated_improved_pit</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
           <t>host_family</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>cooking_set</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>water_intermittent</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="C8" t="inlineStr">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>guardian</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>ceramic_tiles</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>plywood</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>cardboard</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>unprotected_well</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>pit_latrine_with_slab</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
         <is>
           <t>rented_accommodation</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>jerrycan</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>electricity_intermittent</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="C9" t="inlineStr">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>caregiver</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>cement</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>cardboard</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>metal</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>protected_spring</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>pit_latrine_without_slab</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
         <is>
           <t>displacement_site</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>clothing</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>sanitation_overflowing</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="C10" t="inlineStr">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>dependent</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>carpet</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>reused_wood</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>wood</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>unprotected_spring</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>composting_toilet</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
         <is>
           <t>unsheltered</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>solar_lantern</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="C11" t="inlineStr">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>in_law</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>cement</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>calamine_cement_fiber</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>rainwater</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>bucket_latrine</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
         <is>
           <t>camp_planned</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>hygiene_kit</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="C12" t="inlineStr">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>extended_family</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>stone_with_lime_cement</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>ceramic_tiles</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>tanker_truck</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>hanging_toilet</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
         <is>
           <t>spontaneous_settlement</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>winterization_kit</t>
         </is>
       </c>
     </row>
     <row r="13">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>payment_proxy</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
+          <t>bricks</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>cement</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>cart_with_small_tank</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>open_defecation</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
           <t>cooking_pot</t>
         </is>
       </c>
     </row>
     <row r="14">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>survivor</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
+          <t>cement_blocks</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>roofing_shingles</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>surface_water</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
           <t>plate_or_bowl</t>
         </is>
       </c>
     </row>
     <row r="15">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>non_relative</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
+          <t>covered_adobe</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>bottled_water</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
           <t>cup_or_mug</t>
         </is>
       </c>
     </row>
     <row r="16">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
+        <is>
+          <t>wood_planks_shingles</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>packaged_water</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
         <is>
           <t>kitchen_knife</t>
         </is>
@@ -1242,47 +1766,57 @@
     <row r="17">
       <c r="E17" t="inlineStr">
         <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
           <t>matches_or_lighter</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="E18" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>mosquito_net</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="E19" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>clothing_adult</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="E20" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t>clothing_child</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="E21" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t>shelter_repair_tools</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="E22" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t>water_jerrycan</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="E23" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t>other</t>
         </is>
